--- a/3-能力管理/运行记录类文件/030204-2025年7-2026年4月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年7-2026年4月运维服务能力改进计划及跟踪.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowHeight="18180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>2025年7月-2026年4月运维服务能力改进计划及跟踪</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>跟踪中</t>
+  </si>
+  <si>
+    <t>赵维涵</t>
   </si>
   <si>
     <t>满意度调查报告客户反馈</t>
@@ -1120,16 +1123,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="25.5" customWidth="1"/>
-    <col min="3" max="3" width="11.8796296296296" customWidth="1"/>
-    <col min="4" max="4" width="17.8796296296296" customWidth="1"/>
-    <col min="5" max="5" width="26.6296296296296" customWidth="1"/>
+    <col min="3" max="3" width="11.8833333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.8833333333333" customWidth="1"/>
+    <col min="5" max="5" width="26.6333333333333" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="7" width="13.6296296296296" customWidth="1"/>
+    <col min="7" max="7" width="13.6333333333333" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.3796296296296" customWidth="1"/>
+    <col min="9" max="9" width="12.3833333333333" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1227,7 +1230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="86.4" spans="1:10">
+    <row r="5" ht="77.25" spans="1:10">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -1256,24 +1259,24 @@
         <v>28</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="6" ht="100.8" spans="1:10">
+    <row r="6" ht="89.25" spans="1:10">
       <c r="A6" s="8">
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>17</v>
@@ -1288,7 +1291,7 @@
         <v>28</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
